--- a/data/UK-BDI-2025-plants-wider-countryside.xlsx
+++ b/data/UK-BDI-2025-plants-wider-countryside.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\balint.szilagyi\york_msc\aai_summative\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30AC5ACD-D769-49D3-88B8-FEE223579B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4173738-B138-4387-A5C6-09537AB6448D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="12645" xr2:uid="{C564B5EC-3318-41F7-A3E9-C9A627B9C4A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="567" activeTab="4" xr2:uid="{C564B5EC-3318-41F7-A3E9-C9A627B9C4A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover_sheet" sheetId="1" r:id="rId1"/>
@@ -1511,7 +1511,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1573,6 +1573,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2178,9 +2181,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="22" t="s">
         <v>32</v>
       </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
@@ -2938,6 +2946,9 @@
       <c r="F46" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
   <headerFooter>
